--- a/output/full_scan/batch_seq1_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1455</v>
+        <v>1236</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>757.3673003356236</v>
+        <v>703.2297108069665</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.9</v>
+        <v>25.55</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.20551031752308</v>
+        <v>66.7087465265877</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.90274183547051</v>
+        <v>17.97436836412685</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.763187470986342</v>
+        <v>2.922971080696647</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.07986867141642801</v>
+        <v>0.2541753508752016</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1236</v>
+        <v>1432</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>703.2297108069665</v>
+        <v>691.6983778071279</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>25.55</v>
+        <v>15.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.7087465265877</v>
+        <v>50.95505930945949</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17.97436836412685</v>
+        <v>27.14900296454418</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.922971080696647</v>
+        <v>1.834868127964089</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2541753508752016</v>
+        <v>0.07686882461836959</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>691.6983778071279</v>
+        <v>655.4176466223271</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15.3</v>
+        <v>13.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>50.95505930945949</v>
+        <v>61.99050824398894</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.14900296454418</v>
+        <v>19.1335245225969</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.834868127964089</v>
+        <v>3.064735123067924</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.07686882461836959</v>
+        <v>0.07283466110814039</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1459</v>
+        <v>1315</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>681.859226274169</v>
+        <v>641.9776525161909</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>82.5446517378094</v>
+        <v>56.81657250339161</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.77110469516426</v>
+        <v>22.14191751707056</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.616844559706748</v>
+        <v>3.632268463548592</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1920748616487319</v>
+        <v>-0.0390980262501786</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1440</v>
+        <v>1414</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>655.4176466223271</v>
+        <v>604.4073922136967</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13.5</v>
+        <v>19.75</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>61.99050824398894</v>
+        <v>62.65579506302176</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19.1335245225969</v>
+        <v>21.37882945360189</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.064735123067924</v>
+        <v>2.235128564540081</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.07283466110814039</v>
+        <v>0.08557494286326089</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1315</v>
+        <v>1101</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>641.9776525161909</v>
+        <v>575.5490231738488</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>24.55</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.81657250339161</v>
+        <v>56.64948156505591</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.14191751707056</v>
+        <v>20.36691441361069</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.632268463548592</v>
+        <v>0.5201025444342581</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.0390980262501786</v>
+        <v>0.0590372878310092</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1414</v>
+        <v>1232</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>604.4073922136967</v>
+        <v>564.6980285091774</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.75</v>
+        <v>156</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>62.65579506302176</v>
+        <v>55.35487568304195</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.37882945360189</v>
+        <v>30.70655336152507</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.235128564540081</v>
+        <v>0.5241001510086829</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.08557494286326089</v>
+        <v>-0.2673496964089494</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1470</v>
+        <v>1313</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>604.2458481681259</v>
+        <v>555.3260233659473</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>23.4</v>
+        <v>11.6</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>54.10735258036667</v>
+        <v>50.77905797682224</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6.465114737637247</v>
+        <v>20.14945585728034</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.662092211387986</v>
+        <v>0.4742205420522981</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.1122262956772385</v>
+        <v>0.0276307522080774</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1101</v>
+        <v>1341</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>575.5490231738488</v>
+        <v>513.7700600064557</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>24.55</v>
+        <v>59.2</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.64948156505591</v>
+        <v>51.88819546590874</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>20.36691441361069</v>
+        <v>8.110488357944856</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5201025444342581</v>
+        <v>5.399576926899215</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0590372878310092</v>
+        <v>0.224228204884191</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1232</v>
+        <v>1439</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>564.6980285091774</v>
+        <v>503.3813703424971</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>156</v>
+        <v>29.25</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.35487568304195</v>
+        <v>64.85075396768907</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.70655336152507</v>
+        <v>16.03965461945745</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5241001510086829</v>
+        <v>0.8500429598142515</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.2673496964089494</v>
+        <v>0.1711707703781232</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1313</v>
+        <v>1303</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>555.3260233659473</v>
+        <v>500.4980581565095</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11.6</v>
+        <v>185</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>50.77905797682224</v>
+        <v>55.42428407817741</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.14945585728034</v>
+        <v>20.52025204411338</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4742205420522981</v>
+        <v>1.007966789273589</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0276307522080774</v>
+        <v>-0.7805570224379466</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1341</v>
+        <v>1319</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>513.7700600064557</v>
+        <v>485.6500665989697</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>59.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.88819546590874</v>
+        <v>56.35582931772392</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8.110488357944856</v>
+        <v>28.60647410663972</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5.399576926899215</v>
+        <v>0.8193837950818516</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.224228204884191</v>
+        <v>1.148480697800831</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1451</v>
+        <v>1339</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>506.0613994428517</v>
+        <v>480.1559846262623</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>17.5</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.58622648387279</v>
+        <v>57.16197247335165</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10.86194188305367</v>
+        <v>14.56773931019032</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.514010492516625</v>
+        <v>1.187165645583395</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0018392389453406</v>
+        <v>0.0476609489042782</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1439</v>
+        <v>1210</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>503.3813703424971</v>
+        <v>479.5083927896319</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>29.25</v>
+        <v>53.2</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.85075396768907</v>
+        <v>32.86049962516466</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>16.03965461945745</v>
+        <v>30.74082274022887</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8500429598142515</v>
+        <v>0.9375463493128898</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1711707703781232</v>
+        <v>-0.5709434603430353</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1303</v>
+        <v>1442</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>500.4980581565095</v>
+        <v>463.9961152194388</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>185</v>
+        <v>30.05</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.42428407817741</v>
+        <v>59.77732465251191</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.52025204411338</v>
+        <v>24.51200846444699</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.007966789273589</v>
+        <v>0.569529655563828</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.7805570224379466</v>
+        <v>-0.0417638271701314</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1319</v>
+        <v>1434</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>485.6500665989697</v>
+        <v>460.1066782281397</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.35582931772392</v>
+        <v>49.32733178186417</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.60647410663972</v>
+        <v>27.25084531355139</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8193837950818516</v>
+        <v>0.31224132678664</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.148480697800831</v>
+        <v>-0.1668983153701756</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>480.1559846262623</v>
+        <v>450.2045376049264</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45</v>
+        <v>5.26</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>57.16197247335165</v>
+        <v>50.58992665982871</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14.56773931019032</v>
+        <v>15.16164869552063</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.187165645583395</v>
+        <v>2.447087424038074</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0476609489042782</v>
+        <v>0.0117913592277117</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1210</v>
+        <v>1402</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>479.5083927896319</v>
+        <v>431.4865867818972</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>53.2</v>
+        <v>27.25</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>32.86049962516466</v>
+        <v>48.53208252447895</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.74082274022887</v>
+        <v>14.98265544392255</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.9375463493128898</v>
+        <v>0.8748666103322199</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.5709434603430353</v>
+        <v>0.007885730520667</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1442</v>
+        <v>1233</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>463.9961152194388</v>
+        <v>429.9782956728216</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>30.05</v>
+        <v>28.3</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.77732465251191</v>
+        <v>41.86551191468388</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24.51200846444699</v>
+        <v>33.6021529909022</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.569529655563828</v>
+        <v>2.619678594547713</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0417638271701314</v>
+        <v>-0.0725043229866663</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, cci_momentum, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1434</v>
+        <v>1326</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>460.1066782281397</v>
+        <v>417.614022118259</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>17.7</v>
+        <v>58.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>49.32733178186417</v>
+        <v>46.72364786741233</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27.25084531355139</v>
+        <v>16.18149206215964</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.31224132678664</v>
+        <v>0.3033480001258474</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1668983153701756</v>
+        <v>-0.9563567661736904</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1340</v>
+        <v>1216</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>450.2045376049264</v>
+        <v>406.1878362618413</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>5.26</v>
+        <v>75.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.58992665982871</v>
+        <v>48.45395477220026</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15.16164869552063</v>
+        <v>22.4434292159452</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.447087424038074</v>
+        <v>0.464845413487146</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0117913592277117</v>
+        <v>-0.3292378673129482</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1402</v>
+        <v>1321</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>431.4865867818972</v>
+        <v>405.1500315263117</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>27.25</v>
+        <v>32.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>48.53208252447895</v>
+        <v>55.99938031814563</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14.98265544392255</v>
+        <v>15.70932028320646</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8748666103322199</v>
+        <v>0.8976667640478442</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.007885730520667</v>
+        <v>-0.0642099183046726</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1233</v>
+        <v>1325</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>429.9782956728216</v>
+        <v>399.9170857301813</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>28.3</v>
+        <v>26.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>41.86551191468388</v>
+        <v>54.47035041618717</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>33.6021529909022</v>
+        <v>24.42973529382042</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>2.619678594547713</v>
+        <v>0.641140510517171</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.0725043229866663</v>
+        <v>0.0417923298712714</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1477</v>
+        <v>1203</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>420.2922320887714</v>
+        <v>396.2487646111425</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>222</v>
+        <v>46.15</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.08380708552622</v>
+        <v>47.85060401342729</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.386146970221</v>
+        <v>16.55332518785111</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.988532649858242</v>
+        <v>0.4412605718888441</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.8357986571076184</v>
+        <v>-0.2593357108609584</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1326</v>
+        <v>1409</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>417.614022118259</v>
+        <v>392.597525396081</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>58.8</v>
+        <v>24.75</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46.72364786741233</v>
+        <v>55.13721254424407</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16.18149206215964</v>
+        <v>19.44434047033464</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3033480001258474</v>
+        <v>0.4383257877322477</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.9563567661736904</v>
+        <v>0.1834661644622681</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1216</v>
+        <v>1416</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>406.1878362618413</v>
+        <v>384.7666510627297</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>75.5</v>
+        <v>11</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>48.45395477220026</v>
+        <v>52.85143311864272</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.4434292159452</v>
+        <v>23.30663987437248</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.464845413487146</v>
+        <v>0.7952850740952428</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.3292378673129482</v>
+        <v>0.0164691298119445</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1321</v>
+        <v>1435</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>405.1500315263117</v>
+        <v>380.7183489847618</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>32.2</v>
+        <v>24.65</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.99938031814563</v>
+        <v>54.16748534252914</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.70932028320646</v>
+        <v>7.8875490254507</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8976667640478442</v>
+        <v>1.012777007365202</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0642099183046726</v>
+        <v>-0.1133467780403024</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1325</v>
+        <v>1301</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>399.9170857301813</v>
+        <v>377.3268795199679</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>26.8</v>
+        <v>55.6</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.47035041618717</v>
+        <v>46.74057285264729</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.42973529382042</v>
+        <v>16.2879639242656</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.641140510517171</v>
+        <v>0.2362339721304926</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0417923298712714</v>
+        <v>-0.826125254648997</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1468</v>
+        <v>1529</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>397.9058360873087</v>
+        <v>375.3317305779123</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>13.55</v>
+        <v>17.15</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>54.54455687386226</v>
+        <v>30.08471933143115</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.29357225568403</v>
+        <v>35.58055901519018</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.790169614439386</v>
+        <v>0.4782492879536094</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0481706558958541</v>
+        <v>0.0234889353503895</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1203</v>
+        <v>1312</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>396.2487646111425</v>
+        <v>374.406842402978</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>46.15</v>
+        <v>11.9</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.85060401342729</v>
+        <v>43.60015075934464</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16.55332518785111</v>
+        <v>15.03698405684349</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4412605718888441</v>
+        <v>0.3408073090038997</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.2593357108609584</v>
+        <v>-0.0116080394501703</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1409</v>
+        <v>1437</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>392.597525396081</v>
+        <v>372.0820675344497</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>24.75</v>
+        <v>30.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.13721254424407</v>
+        <v>47.24111028021072</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.44434047033464</v>
+        <v>20.3630530643049</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4383257877322477</v>
+        <v>0.753519599408532</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1834661644622681</v>
+        <v>-0.193574602873398</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1416</v>
+        <v>1438</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>384.7666510627297</v>
+        <v>324.0965284716901</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11</v>
+        <v>22.45</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.85143311864272</v>
+        <v>52.23340089418358</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23.30663987437248</v>
+        <v>16.78726608230943</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7952850740952428</v>
+        <v>0.3402546487611793</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0164691298119445</v>
+        <v>0.0225351541154804</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1435</v>
+        <v>1413</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>380.7183489847618</v>
+        <v>321.3740315915614</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>24.65</v>
+        <v>9.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.16748534252914</v>
+        <v>47.89861371233631</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7.8875490254507</v>
+        <v>17.62921728477176</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.012777007365202</v>
+        <v>0.0854226516112757</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.1133467780403024</v>
+        <v>-0.0490512913615632</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1301</v>
+        <v>1443</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>377.3268795199679</v>
+        <v>314.6002671919418</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>55.6</v>
+        <v>26.05</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>46.74057285264729</v>
+        <v>48.6034632756419</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>16.2879639242656</v>
+        <v>10.12622783787222</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.2362339721304926</v>
+        <v>0.3891189433178434</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.826125254648997</v>
+        <v>-0.046063069837107</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1476</v>
+        <v>1215</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>376.6592404515068</v>
+        <v>300.2774813873497</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>337</v>
+        <v>109</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.2547527497449</v>
+        <v>48.76907489427433</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.81431776575</v>
+        <v>46.04018403637832</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7361935825171637</v>
+        <v>0.3217993286505418</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.192501475041352</v>
+        <v>0.6135502568893485</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1529</v>
+        <v>1342</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>375.3317305779123</v>
+        <v>291.370998396547</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>17.15</v>
+        <v>103.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>30.08471933143115</v>
+        <v>44.21683810165703</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>35.58055901519018</v>
+        <v>29.00785181044808</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4782492879536094</v>
+        <v>0.4239649555371862</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0234889353503895</v>
+        <v>-0.5474151602430088</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1312</v>
+        <v>1418</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>374.406842402978</v>
+        <v>289.2806165536698</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11.9</v>
+        <v>18.05</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.60015075934464</v>
+        <v>45.49146964423041</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>15.03698405684349</v>
+        <v>20.9064854849193</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3408073090038997</v>
+        <v>0.07830503393133439</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0116080394501703</v>
+        <v>-0.0469534663168616</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1437</v>
+        <v>1308</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>372.0820675344497</v>
+        <v>288.4512213290426</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>30.3</v>
+        <v>13.65</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>47.24111028021072</v>
+        <v>50.69402639609014</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.3630530643049</v>
+        <v>15.90943347724968</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.753519599408532</v>
+        <v>0.9394717782465584</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.193574602873398</v>
+        <v>0.0128151509991398</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1472</v>
+        <v>1582</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>366.4163875053413</v>
+        <v>285.8165387100873</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.7164746881626</v>
+        <v>50.28894164681002</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10.29541949249131</v>
+        <v>35.70489541579746</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.0993354650464071</v>
+        <v>1.051136203223205</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.289124285613736</v>
+        <v>1.446122500228832</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1514</v>
+        <v>1256</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>363.6186421050177</v>
+        <v>283.4451366287824</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.17686012403858</v>
+        <v>44.11878537641922</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.97785926740444</v>
+        <v>11.75509477151438</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3168205530716353</v>
+        <v>0.3916138227250977</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.5446821632476526</v>
+        <v>-0.5336924677622172</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1475</v>
+        <v>1419</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>349.8601471807221</v>
+        <v>278.4306610938816</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>27.15</v>
+        <v>65</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.1692364591933</v>
+        <v>44.28948633132432</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11.02512044553161</v>
+        <v>18.86836438969267</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.686657122577385</v>
+        <v>0.3417338476106033</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0058837188686939</v>
+        <v>-0.4421405839060781</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1456</v>
+        <v>1309</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>339.9947522869889</v>
+        <v>276.0583100116261</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>14.25</v>
+        <v>12.9</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>55.29907544919909</v>
+        <v>40.23723956517194</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12.22257002089292</v>
+        <v>17.40296942710064</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.083257798382301</v>
+        <v>0.2917132280238245</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0506197359317037</v>
+        <v>-0.0317117757529852</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1513</v>
+        <v>1109</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>324.2229869852226</v>
+        <v>273.1043222575728</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>159.5</v>
+        <v>13.55</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.6690273947666</v>
+        <v>29.25601556227792</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>22.61366654722094</v>
+        <v>38.67690665450619</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4564830819627048</v>
+        <v>0.5623734142682579</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.7513561986088391</v>
+        <v>-0.0075967220492447</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1438</v>
+        <v>1213</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>324.0965284716901</v>
+        <v>269.9862107493723</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>22.45</v>
+        <v>7.72</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.23340089418358</v>
+        <v>54.29196479701656</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.78726608230943</v>
+        <v>11.60638766894242</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3402546487611793</v>
+        <v>1.257765099407753</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0225351541154804</v>
+        <v>0.4108208744957045</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1413</v>
+        <v>1229</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>321.3740315915614</v>
+        <v>266.8431304128908</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>9.4</v>
+        <v>40.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.89861371233631</v>
+        <v>47.8075920985071</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17.62921728477176</v>
+        <v>10.17510902778888</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.0854226516112757</v>
+        <v>0.3668009590548337</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0490512913615632</v>
+        <v>0.004669408092247</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1504</v>
+        <v>1218</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>316.3781351272651</v>
+        <v>258.2295530518275</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>67.2</v>
+        <v>15.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.95803514304393</v>
+        <v>40.91868576962771</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.84301909546548</v>
+        <v>40.21346199077008</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5671647926866603</v>
+        <v>0.4444602904018371</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.3985748316781774</v>
+        <v>0.0402106245470759</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1443</v>
+        <v>1102</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>314.6002671919418</v>
+        <v>250.466188886066</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>26.05</v>
+        <v>32.95</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.6034632756419</v>
+        <v>43.23102006485762</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.12622783787222</v>
+        <v>28.49622213452004</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3891189433178434</v>
+        <v>0.313168107561326</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.046063069837107</v>
+        <v>0.0543479796197455</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1215</v>
+        <v>1220</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>300.2774813873497</v>
+        <v>250.0020168119005</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>109</v>
+        <v>11.15</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.76907489427433</v>
+        <v>33.45802895655817</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46.04018403637832</v>
+        <v>35.44293262152075</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3217993286505418</v>
+        <v>0.9209070604473454</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.6135502568893485</v>
+        <v>-8.611168073738296e-05</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1342</v>
+        <v>1227</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>291.370998396547</v>
+        <v>245.8381839877155</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.5</v>
+        <v>29.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.21683810165703</v>
+        <v>48.0717040356772</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>29.00785181044808</v>
+        <v>17.0434971226909</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4239649555371862</v>
+        <v>0.5514271137051873</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.5474151602430088</v>
+        <v>-0.0781972547635859</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1418</v>
+        <v>1441</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>289.2806165536698</v>
+        <v>245.1699671627625</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18.05</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45.49146964423041</v>
+        <v>41.27370742422021</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>20.9064854849193</v>
+        <v>13.70694282646247</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.07830503393133439</v>
+        <v>0.5856204627494499</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0469534663168616</v>
+        <v>-0.0025880711780282</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1308</v>
+        <v>1446</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>288.4512213290426</v>
+        <v>243.9403894154929</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>13.65</v>
+        <v>13.95</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.69402639609014</v>
+        <v>36.88155938031392</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.90943347724968</v>
+        <v>39.93857748087994</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9394717782465584</v>
+        <v>0.5950848537824609</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0128151509991398</v>
+        <v>0.08705160266745191</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1503</v>
+        <v>1307</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>287.5195043111385</v>
+        <v>243.0278649444217</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>195.5</v>
+        <v>30.9</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.132630185614</v>
+        <v>40.06328869661023</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27.57388656296097</v>
+        <v>18.96074060681871</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5205583736339958</v>
+        <v>3.016380842202621</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.4934480046803884</v>
+        <v>0.08256759283866261</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1582</v>
+        <v>1219</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>285.8165387100873</v>
+        <v>232.9414892178733</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>74.3</v>
+        <v>10.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.28894164681002</v>
+        <v>27.77038990431721</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>35.70489541579746</v>
+        <v>32.71663158633552</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.051136203223205</v>
+        <v>0.7632866989878225</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.446122500228832</v>
+        <v>-0.0714440395496822</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1467</v>
+        <v>1104</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>285.5006060059053</v>
+        <v>232.7995242119793</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>9.789999999999999</v>
+        <v>26.65</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>56.75644467681434</v>
+        <v>44.87824843189272</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.30029682107356</v>
+        <v>15.9596395864901</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4028030476834224</v>
+        <v>0.843243082377041</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.07109102824776781</v>
+        <v>0.0295127971626206</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1256</v>
+        <v>1305</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>283.4451366287824</v>
+        <v>226.9142858345361</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>178</v>
+        <v>11.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.11878537641922</v>
+        <v>44.97214551229173</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.75509477151438</v>
+        <v>20.97826173299758</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3916138227250977</v>
+        <v>0.3470142229252547</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.5336924677622172</v>
+        <v>0.0196150097396708</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1506</v>
+        <v>1231</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>283.3261387596981</v>
+        <v>224.5097175152215</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10.5</v>
+        <v>80.3</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.17493080517829</v>
+        <v>31.87408791399382</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.52701872264269</v>
+        <v>25.98211034398228</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.083977083971008</v>
+        <v>0.3953534595738895</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.0357127458480727</v>
+        <v>-0.995768995764412</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1464</v>
+        <v>1338</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>283.0649680847349</v>
+        <v>219.9430965182523</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10.4</v>
+        <v>15.45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.37862875258937</v>
+        <v>40.78504905153831</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.40783265754652</v>
+        <v>35.16739006497221</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8557306713035857</v>
+        <v>1.142809366382123</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0062496728966701</v>
+        <v>-0.0130538811846954</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1419</v>
+        <v>1225</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>278.4306610938816</v>
+        <v>211.1993201327839</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>44.28948633132432</v>
+        <v>38.86130286821421</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.86836438969267</v>
+        <v>33.55389528715855</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3417338476106033</v>
+        <v>0.7875814786139048</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.4421405839060781</v>
+        <v>-0.09092394921692599</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1309</v>
+        <v>1444</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>276.0583100116261</v>
+        <v>208.5972347698317</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>12.9</v>
+        <v>7.26</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.23723956517194</v>
+        <v>42.16042728975016</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.40296942710064</v>
+        <v>18.18754672831286</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2917132280238245</v>
+        <v>0.4560211467935046</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0317117757529852</v>
+        <v>-0.0712719406507603</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1466</v>
+        <v>1314</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>273.9799855036688</v>
+        <v>199.6871860740196</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>17</v>
+        <v>7.74</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.11409813460498</v>
+        <v>42.48497000722318</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.71294961773311</v>
+        <v>17.00316718961778</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3900230198637866</v>
+        <v>1.050157422568513</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.068655337603724</v>
+        <v>-0.0427690497566308</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1109</v>
+        <v>1447</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>273.1043222575728</v>
+        <v>199.607444136403</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>13.55</v>
+        <v>7.17</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>29.25601556227792</v>
+        <v>47.86790841357237</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>38.67690665450619</v>
+        <v>18.43821484954216</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5623734142682579</v>
+        <v>0.5361979764636715</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0075967220492447</v>
+        <v>-0.0678063562122455</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1452</v>
+        <v>1217</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>272.53804527442</v>
+        <v>179.9396072121974</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11.35</v>
+        <v>9.84</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.70541174058715</v>
+        <v>45.39555803639406</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.56070525493503</v>
+        <v>13.93618935610581</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.149108471785315</v>
+        <v>0.5581095265827097</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0387139697589639</v>
+        <v>-0.022520464982911</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1213</v>
+        <v>1108</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>269.9862107493723</v>
+        <v>174.5345241714738</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>7.72</v>
+        <v>12.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>54.29196479701656</v>
+        <v>34.41076451086226</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11.60638766894242</v>
+        <v>55.36989798129499</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.257765099407753</v>
+        <v>0.8113937266295244</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.4108208744957045</v>
+        <v>0.0474161179808466</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1516</v>
+        <v>1436</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>268.7660046250556</v>
+        <v>171.6052586390423</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>14.65</v>
+        <v>37.35</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>29.32996916303696</v>
+        <v>36.65199757600755</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>56.61051752521329</v>
+        <v>38.00720489137337</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7141285405674545</v>
+        <v>0.3856345435295237</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.036560205688965</v>
+        <v>-0.035652015987003</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1229</v>
+        <v>1471</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>266.8431304128908</v>
+        <v>158.7118920932218</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>40.7</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.8075920985071</v>
+        <v>40.13540684741768</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.17510902778888</v>
+        <v>30.38319359370931</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3668009590548337</v>
+        <v>0.5002555998375006</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.004669408092247</v>
+        <v>0.0314117826080745</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1218</v>
+        <v>1310</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>258.2295530518275</v>
+        <v>156.2236749125234</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15.8</v>
+        <v>8.08</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.91868576962771</v>
+        <v>40.86156533978302</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>40.21346199077008</v>
+        <v>25.47141747180627</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4444602904018371</v>
+        <v>0.5984649742506316</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0402106245470759</v>
+        <v>-0.0797768376223008</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1102</v>
+        <v>1417</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>250.466188886066</v>
+        <v>147.9698196550612</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>32.95</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>43.23102006485762</v>
+        <v>41.64525589946581</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.49622213452004</v>
+        <v>17.56455094982805</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.313168107561326</v>
+        <v>0.4027821031869614</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0543479796197455</v>
+        <v>-0.0191155766993819</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1220</v>
+        <v>1324</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>250.0020168119005</v>
+        <v>145.9356377683807</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11.15</v>
+        <v>10.05</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>33.45802895655817</v>
+        <v>40.73859757124411</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>35.44293262152075</v>
+        <v>20.95891146280975</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9209070604473454</v>
+        <v>0.6255134998486527</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-8.611168073738296e-05</v>
+        <v>-0.0052202098945228</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1227</v>
+        <v>1569</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>245.8381839877155</v>
+        <v>130.4734534793553</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>29.2</v>
+        <v>42.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.0717040356772</v>
+        <v>47.83858461925863</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.0434971226909</v>
+        <v>22.14611431496472</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5514271137051873</v>
+        <v>0.1998816790266702</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0781972547635859</v>
+        <v>0.5179042610389324</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1441</v>
+        <v>1304</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>245.1699671627625</v>
+        <v>127.8085342397576</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.27370742422021</v>
+        <v>46.31273272304497</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.70694282646247</v>
+        <v>16.91914215687644</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5856204627494499</v>
+        <v>0.473317417440935</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0025880711780282</v>
+        <v>-0.0068070893827432</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1446</v>
+        <v>1316</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>243.9403894154929</v>
+        <v>126.8937502594822</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>13.95</v>
+        <v>10.05</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.88155938031392</v>
+        <v>46.41944271004673</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>39.93857748087994</v>
+        <v>18.65139964539589</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5950848537824609</v>
+        <v>0.6784657644414619</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.08705160266745191</v>
+        <v>0.0221929073989992</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1307</v>
+        <v>1423</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>243.0278649444217</v>
+        <v>113.3934304045662</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>30.9</v>
+        <v>35.95</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>40.06328869661023</v>
+        <v>41.49654951178776</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.96074060681871</v>
+        <v>14.32724214360599</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>3.016380842202621</v>
+        <v>0.1583397159536261</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.08256759283866261</v>
+        <v>0.162432418309294</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1473</v>
+        <v>1201</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>233.0713426330989</v>
+        <v>108.3261391825892</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>19.95</v>
+        <v>12.15</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.54303012491582</v>
+        <v>43.34153673638144</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10.09595419265627</v>
+        <v>14.99755037619781</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.241002521360708</v>
+        <v>0.5234775377026394</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0028982281949641</v>
+        <v>-0.0335802860264326</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1219</v>
+        <v>1103</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>232.9414892178733</v>
+        <v>95.61966897669269</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10.8</v>
+        <v>13.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>27.77038990431721</v>
+        <v>46.84546754370454</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>32.71663158633552</v>
+        <v>10.23609066997606</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7632866989878225</v>
+        <v>0.3869830144951806</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0714440395496822</v>
+        <v>-0.0128442084784236</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1104</v>
+        <v>1410</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>232.7995242119793</v>
+        <v>75.51857357338592</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>26.65</v>
+        <v>25.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.87824843189272</v>
+        <v>48.90140683300331</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15.9596395864901</v>
+        <v>16.04508207501541</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.843243082377041</v>
+        <v>0.7234906401397504</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0295127971626206</v>
+        <v>-0.0141289588810439</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1305</v>
+        <v>1445</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>226.9142858345361</v>
+        <v>65.61490006770882</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11.7</v>
+        <v>10.45</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.97214551229173</v>
+        <v>39.49891678641576</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.97826173299758</v>
+        <v>15.31297395805671</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3470142229252547</v>
+        <v>0.7311005453782687</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,1546 +4651,9 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0196150097396708</v>
+        <v>-0.0275302750137435</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>1231</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>聯華食</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>224.5097175152215</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>31.87408791399382</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>25.98211034398228</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>0.3953534595738895</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>-0.995768995764412</v>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>1338</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>廣華-KY</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>219.9430965182523</v>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>15.45</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>40.78504905153831</v>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>35.16739006497221</v>
-      </c>
-      <c r="J81" s="2" t="n">
-        <v>1.142809366382123</v>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N81" s="2" t="n">
-        <v>-0.0130538811846954</v>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>1225</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>福懋油</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>211.1993201327839</v>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>38.86130286821421</v>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>33.55389528715855</v>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>0.7875814786139048</v>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N82" s="2" t="n">
-        <v>-0.09092394921692599</v>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>1444</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>力麗</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>208.5972347698317</v>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>42.16042728975016</v>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>18.18754672831286</v>
-      </c>
-      <c r="J83" s="2" t="n">
-        <v>0.4560211467935046</v>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" s="2" t="n">
-        <v>-0.0712719406507603</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>1463</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>強盛新</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D84" s="2" t="n">
-        <v>207.991945057892</v>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>50.76088194108512</v>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>14.8167394142925</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>0.4341733568450631</v>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>-0.006948352579218</v>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>1314</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>中石化</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D85" s="2" t="n">
-        <v>199.6871860740196</v>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>7.74</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="2" t="n">
-        <v>42.48497000722318</v>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>17.00316718961778</v>
-      </c>
-      <c r="J85" s="2" t="n">
-        <v>1.050157422568513</v>
-      </c>
-      <c r="K85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N85" s="2" t="n">
-        <v>-0.0427690497566308</v>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>1447</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>力鵬</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D86" s="2" t="n">
-        <v>199.607444136403</v>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>47.86790841357237</v>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>18.43821484954216</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>0.5361979764636715</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>-0.0678063562122455</v>
-      </c>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>1457</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>宜進</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D87" s="2" t="n">
-        <v>192.0487638205085</v>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>41.86339650791077</v>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>15.8335937942792</v>
-      </c>
-      <c r="J87" s="2" t="n">
-        <v>0.6850945235481462</v>
-      </c>
-      <c r="K87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N87" s="2" t="n">
-        <v>-0.0220599379196323</v>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>1217</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>愛之味</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D88" s="2" t="n">
-        <v>179.9396072121974</v>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>45.39555803639406</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>13.93618935610581</v>
-      </c>
-      <c r="J88" s="2" t="n">
-        <v>0.5581095265827097</v>
-      </c>
-      <c r="K88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N88" s="2" t="n">
-        <v>-0.022520464982911</v>
-      </c>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>1108</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>幸福</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D89" s="2" t="n">
-        <v>174.5345241714738</v>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>34.41076451086226</v>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>55.36989798129499</v>
-      </c>
-      <c r="J89" s="2" t="n">
-        <v>0.8113937266295244</v>
-      </c>
-      <c r="K89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N89" s="2" t="n">
-        <v>0.0474161179808466</v>
-      </c>
-      <c r="O89" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>1436</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>華友聯</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D90" s="2" t="n">
-        <v>171.6052586390423</v>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>36.65199757600755</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>38.00720489137337</v>
-      </c>
-      <c r="J90" s="2" t="n">
-        <v>0.3856345435295237</v>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N90" s="2" t="n">
-        <v>-0.035652015987003</v>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>1460</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>宏遠</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D91" s="2" t="n">
-        <v>170.4541957656101</v>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2" t="n">
-        <v>40.98329909524027</v>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>18.83980739084251</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>0.4252015352218735</v>
-      </c>
-      <c r="K91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>-0.0158873217211047</v>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>1465</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>偉全</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D92" s="2" t="n">
-        <v>169.4294127515488</v>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>12.35</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>43.0576444908244</v>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>16.29144518610978</v>
-      </c>
-      <c r="J92" s="2" t="n">
-        <v>0.9129549811358983</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N92" s="2" t="n">
-        <v>-0.0505312684332952</v>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>1471</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>首利</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D93" s="2" t="n">
-        <v>158.7118920932218</v>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>40.13540684741768</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>30.38319359370931</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>0.5002555998375006</v>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N93" s="2" t="n">
-        <v>0.0314117826080745</v>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>1310</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>台苯</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D94" s="2" t="n">
-        <v>156.2236749125234</v>
-      </c>
-      <c r="E94" s="2" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>40.86156533978302</v>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>25.47141747180627</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>0.5984649742506316</v>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N94" s="2" t="n">
-        <v>-0.0797768376223008</v>
-      </c>
-      <c r="O94" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>1417</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>嘉裕</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D95" s="2" t="n">
-        <v>147.9698196550612</v>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>41.64525589946581</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>17.56455094982805</v>
-      </c>
-      <c r="J95" s="2" t="n">
-        <v>0.4027821031869614</v>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N95" s="2" t="n">
-        <v>-0.0191155766993819</v>
-      </c>
-      <c r="O95" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>1324</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>地球</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D96" s="2" t="n">
-        <v>145.9356377683807</v>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>40.73859757124411</v>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>20.95891146280975</v>
-      </c>
-      <c r="J96" s="2" t="n">
-        <v>0.6255134998486527</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N96" s="2" t="n">
-        <v>-0.0052202098945228</v>
-      </c>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>1453</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>大將</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D97" s="2" t="n">
-        <v>145.9210058694918</v>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>45.4797091797211</v>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>11.73743997185176</v>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>1.169250743119128</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N97" s="2" t="n">
-        <v>0.0071663305601247</v>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>1569</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>濱川</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D98" s="2" t="n">
-        <v>130.4734534793553</v>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>47.83858461925863</v>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>22.14611431496472</v>
-      </c>
-      <c r="J98" s="2" t="n">
-        <v>0.1998816790266702</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>0.5179042610389324</v>
-      </c>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>1304</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>台聚</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D99" s="2" t="n">
-        <v>127.8085342397576</v>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>46.31273272304497</v>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>16.91914215687644</v>
-      </c>
-      <c r="J99" s="2" t="n">
-        <v>0.473317417440935</v>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N99" s="2" t="n">
-        <v>-0.0068070893827432</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>1316</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>上曜</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D100" s="2" t="n">
-        <v>126.8937502594822</v>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>46.41944271004673</v>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>18.65139964539589</v>
-      </c>
-      <c r="J100" s="2" t="n">
-        <v>0.6784657644414619</v>
-      </c>
-      <c r="K100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>0.0221929073989992</v>
-      </c>
-      <c r="O100" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>1423</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>利華</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D101" s="2" t="n">
-        <v>113.3934304045662</v>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>35.95</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>41.49654951178776</v>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>14.32724214360599</v>
-      </c>
-      <c r="J101" s="2" t="n">
-        <v>0.1583397159536261</v>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N101" s="2" t="n">
-        <v>0.162432418309294</v>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>1201</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>味全</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D102" s="2" t="n">
-        <v>108.3261391825892</v>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>43.34153673638144</v>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>14.99755037619781</v>
-      </c>
-      <c r="J102" s="2" t="n">
-        <v>0.5234775377026394</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>-0.0335802860264326</v>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>1454</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>台富</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D103" s="2" t="n">
-        <v>98.92490862704636</v>
-      </c>
-      <c r="E103" s="2" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>47.64033557561956</v>
-      </c>
-      <c r="I103" s="2" t="n">
-        <v>13.07255500597023</v>
-      </c>
-      <c r="J103" s="2" t="n">
-        <v>0.980920530279335</v>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N103" s="2" t="n">
-        <v>0.0145986486995214</v>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>1512</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>瑞利</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D104" s="2" t="n">
-        <v>95.62716965337351</v>
-      </c>
-      <c r="E104" s="2" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>39.00784373060181</v>
-      </c>
-      <c r="I104" s="2" t="n">
-        <v>8.16287252794978</v>
-      </c>
-      <c r="J104" s="2" t="n">
-        <v>0.6572700064246204</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N104" s="2" t="n">
-        <v>-0.009451427329417301</v>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>1103</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>嘉泥</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D105" s="2" t="n">
-        <v>95.61966897669269</v>
-      </c>
-      <c r="E105" s="2" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>46.84546754370454</v>
-      </c>
-      <c r="I105" s="2" t="n">
-        <v>10.23609066997606</v>
-      </c>
-      <c r="J105" s="2" t="n">
-        <v>0.3869830144951806</v>
-      </c>
-      <c r="K105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N105" s="2" t="n">
-        <v>-0.0128442084784236</v>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>1474</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>弘裕</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>89.72239777675033</v>
-      </c>
-      <c r="E106" s="2" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>44.02569486509021</v>
-      </c>
-      <c r="I106" s="2" t="n">
-        <v>18.35981444589195</v>
-      </c>
-      <c r="J106" s="2" t="n">
-        <v>0.5430110537321322</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>-0.0391845374018095</v>
-      </c>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>1410</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>南染</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D107" s="2" t="n">
-        <v>75.51857357338592</v>
-      </c>
-      <c r="E107" s="2" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>48.90140683300331</v>
-      </c>
-      <c r="I107" s="2" t="n">
-        <v>16.04508207501541</v>
-      </c>
-      <c r="J107" s="2" t="n">
-        <v>0.7234906401397504</v>
-      </c>
-      <c r="K107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N107" s="2" t="n">
-        <v>-0.0141289588810439</v>
-      </c>
-      <c r="O107" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>1445</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>大宇</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D108" s="2" t="n">
-        <v>65.61490006770882</v>
-      </c>
-      <c r="E108" s="2" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>39.49891678641576</v>
-      </c>
-      <c r="I108" s="2" t="n">
-        <v>15.31297395805671</v>
-      </c>
-      <c r="J108" s="2" t="n">
-        <v>0.7311005453782687</v>
-      </c>
-      <c r="K108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N108" s="2" t="n">
-        <v>-0.0275302750137435</v>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq1_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1323</v>
+        <v>1455</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>964.9070025824826</v>
+        <v>1067.367300335624</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>21.6</v>
+        <v>9.9</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>74.37303074133898</v>
+        <v>64.20551031752308</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16.71228586506538</v>
+        <v>17.90274183547051</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6.327402811194125</v>
+        <v>4.763187470986342</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1067322343013938</v>
+        <v>0.07986867141642801</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1110</v>
+        <v>1323</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>847.9296608341025</v>
+        <v>964.9070025824826</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16.3</v>
+        <v>21.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.16977240725036</v>
+        <v>74.37303074133898</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.99443637730544</v>
+        <v>16.71228586506538</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.673177439138842</v>
+        <v>6.327402811194125</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.0159813843765176</v>
+        <v>0.1067322343013938</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1236</v>
+        <v>1459</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>703.2297108069665</v>
+        <v>871.859226274169</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25.55</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.7087465265877</v>
+        <v>82.5446517378094</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.97436836412685</v>
+        <v>23.77110469516426</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.922971080696647</v>
+        <v>1.616844559706748</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2541753508752016</v>
+        <v>0.1920748616487319</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1432</v>
+        <v>1110</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>691.6983778071279</v>
+        <v>847.9296608341025</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15.3</v>
+        <v>16.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>50.95505930945949</v>
+        <v>61.16977240725036</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>27.14900296454418</v>
+        <v>31.99443637730544</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.834868127964089</v>
+        <v>1.673177439138842</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07686882461836959</v>
+        <v>-0.0159813843765176</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1440</v>
+        <v>1525</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>655.4176466223271</v>
+        <v>750.4106624099597</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.99050824398894</v>
+        <v>57.085860380981</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19.1335245225969</v>
+        <v>38.34359119274299</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.064735123067924</v>
+        <v>0.6319071688778813</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.07283466110814039</v>
+        <v>0.0571250714364731</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1315</v>
+        <v>1236</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>641.9776525161909</v>
+        <v>703.2297108069665</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>25.55</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.81657250339161</v>
+        <v>66.7087465265877</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.14191751707056</v>
+        <v>17.97436836412685</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.632268463548592</v>
+        <v>2.922971080696647</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.0390980262501786</v>
+        <v>0.2541753508752016</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1414</v>
+        <v>1432</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>604.4073922136967</v>
+        <v>691.6983778071279</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.75</v>
+        <v>15.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>62.65579506302176</v>
+        <v>50.95505930945949</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21.37882945360189</v>
+        <v>27.14900296454418</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.235128564540081</v>
+        <v>1.834868127964089</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.08557494286326089</v>
+        <v>0.07686882461836959</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1101</v>
+        <v>1517</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>575.5490231738488</v>
+        <v>679.6176540260417</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>24.55</v>
+        <v>11.8</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.64948156505591</v>
+        <v>57.91084120801679</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20.36691441361069</v>
+        <v>36.10909017104826</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5201025444342581</v>
+        <v>0.5663445559607702</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0590372878310092</v>
+        <v>-0.0117180875647008</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1232</v>
+        <v>1440</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>564.6980285091774</v>
+        <v>655.4176466223271</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>156</v>
+        <v>13.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>55.35487568304195</v>
+        <v>61.99050824398894</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.70655336152507</v>
+        <v>19.1335245225969</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.5241001510086829</v>
+        <v>3.064735123067924</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.2673496964089494</v>
+        <v>0.07283466110814039</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>555.3260233659473</v>
+        <v>641.9776525161909</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>50.77905797682224</v>
+        <v>56.81657250339161</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.14945585728034</v>
+        <v>22.14191751707056</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4742205420522981</v>
+        <v>3.632268463548592</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0276307522080774</v>
+        <v>-0.0390980262501786</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1341</v>
+        <v>1558</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>513.7700600064557</v>
+        <v>634.0748392381545</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>59.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>51.88819546590874</v>
+        <v>62.21992861161951</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>8.110488357944856</v>
+        <v>18.33942421181917</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5.399576926899215</v>
+        <v>1.024563644019974</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.224228204884191</v>
+        <v>0.20055380639242</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1439</v>
+        <v>1414</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>503.3813703424971</v>
+        <v>604.4073922136967</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29.25</v>
+        <v>19.75</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.85075396768907</v>
+        <v>62.65579506302176</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>16.03965461945745</v>
+        <v>21.37882945360189</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8500429598142515</v>
+        <v>2.235128564540081</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1711707703781232</v>
+        <v>0.08557494286326089</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1303</v>
+        <v>1470</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>500.4980581565095</v>
+        <v>604.2458481681259</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>185</v>
+        <v>23.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.42428407817741</v>
+        <v>54.10735258036667</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.52025204411338</v>
+        <v>6.465114737637247</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.007966789273589</v>
+        <v>0.662092211387986</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.7805570224379466</v>
+        <v>-0.1122262956772385</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1319</v>
+        <v>1537</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>485.6500665989697</v>
+        <v>594.9471823654679</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>77.59999999999999</v>
+        <v>127</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.35582931772392</v>
+        <v>54.63485235213643</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.60647410663972</v>
+        <v>12.67594936996723</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8193837950818516</v>
+        <v>0.8018262682805349</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.148480697800831</v>
+        <v>0.0310161711130878</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1339</v>
+        <v>1101</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>480.1559846262623</v>
+        <v>575.5490231738488</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45</v>
+        <v>24.55</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.16197247335165</v>
+        <v>56.64948156505591</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14.56773931019032</v>
+        <v>20.36691441361069</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.187165645583395</v>
+        <v>0.5201025444342581</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0476609489042782</v>
+        <v>0.0590372878310092</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1210</v>
+        <v>1232</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>479.5083927896319</v>
+        <v>564.6980285091774</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>53.2</v>
+        <v>156</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>32.86049962516466</v>
+        <v>55.35487568304195</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.74082274022887</v>
+        <v>30.70655336152507</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9375463493128898</v>
+        <v>0.5241001510086829</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.5709434603430353</v>
+        <v>-0.2673496964089494</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1442</v>
+        <v>1313</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>463.9961152194388</v>
+        <v>555.3260233659473</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>30.05</v>
+        <v>11.6</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.77732465251191</v>
+        <v>50.77905797682224</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.51200846444699</v>
+        <v>20.14945585728034</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.569529655563828</v>
+        <v>0.4742205420522981</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.0417638271701314</v>
+        <v>0.0276307522080774</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, cci_momentum, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1434</v>
+        <v>1539</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>460.1066782281397</v>
+        <v>544.2750749329914</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>17.7</v>
+        <v>16.35</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>49.32733178186417</v>
+        <v>56.28140055294158</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>27.25084531355139</v>
+        <v>19.73301383492969</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.31224132678664</v>
+        <v>0.5449307075127644</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.1668983153701756</v>
+        <v>0.0051439192044875</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1340</v>
+        <v>1477</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>450.2045376049264</v>
+        <v>535.2922320887715</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5.26</v>
+        <v>222</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>50.58992665982871</v>
+        <v>52.08380708552622</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15.16164869552063</v>
+        <v>12.386146970221</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.447087424038074</v>
+        <v>0.988532649858242</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0117913592277117</v>
+        <v>0.8357986571076184</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1402</v>
+        <v>1341</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>431.4865867818972</v>
+        <v>513.7700600064557</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>27.25</v>
+        <v>59.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>48.53208252447895</v>
+        <v>51.88819546590874</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.98265544392255</v>
+        <v>8.110488357944856</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8748666103322199</v>
+        <v>5.399576926899215</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.007885730520667</v>
+        <v>0.224228204884191</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1233</v>
+        <v>1451</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>429.9782956728216</v>
+        <v>506.0613994428517</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.3</v>
+        <v>17.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>41.86551191468388</v>
+        <v>55.58622648387279</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33.6021529909022</v>
+        <v>10.86194188305367</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.619678594547713</v>
+        <v>1.514010492516625</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0725043229866663</v>
+        <v>0.0018392389453406</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1326</v>
+        <v>1439</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>417.614022118259</v>
+        <v>503.3813703424971</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>58.8</v>
+        <v>29.25</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>46.72364786741233</v>
+        <v>64.85075396768907</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.18149206215964</v>
+        <v>16.03965461945745</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3033480001258474</v>
+        <v>0.8500429598142515</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.9563567661736904</v>
+        <v>0.1711707703781232</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1216</v>
+        <v>1303</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>406.1878362618413</v>
+        <v>500.4980581565095</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>75.5</v>
+        <v>185</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>48.45395477220026</v>
+        <v>55.42428407817741</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.4434292159452</v>
+        <v>20.52025204411338</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.464845413487146</v>
+        <v>1.007966789273589</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.3292378673129482</v>
+        <v>-0.7805570224379466</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1321</v>
+        <v>1476</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>405.1500315263117</v>
+        <v>491.6592404515068</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>32.2</v>
+        <v>337</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.99938031814563</v>
+        <v>47.2547527497449</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.70932028320646</v>
+        <v>20.81431776575</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8976667640478442</v>
+        <v>0.7361935825171637</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0642099183046726</v>
+        <v>0.192501475041352</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1325</v>
+        <v>1319</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>399.9170857301813</v>
+        <v>485.6500665989697</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.47035041618717</v>
+        <v>56.35582931772392</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>24.42973529382042</v>
+        <v>28.60647410663972</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.641140510517171</v>
+        <v>0.8193837950818516</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0417923298712714</v>
+        <v>1.148480697800831</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1203</v>
+        <v>1339</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>396.2487646111425</v>
+        <v>480.1559846262623</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>46.15</v>
+        <v>45</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>47.85060401342729</v>
+        <v>57.16197247335165</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.55332518785111</v>
+        <v>14.56773931019032</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4412605718888441</v>
+        <v>1.187165645583395</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.2593357108609584</v>
+        <v>0.0476609489042782</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1409</v>
+        <v>1210</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>392.597525396081</v>
+        <v>479.5083927896319</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>24.75</v>
+        <v>53.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.13721254424407</v>
+        <v>32.86049962516466</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.44434047033464</v>
+        <v>30.74082274022887</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4383257877322477</v>
+        <v>0.9375463493128898</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1834661644622681</v>
+        <v>-0.5709434603430353</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1416</v>
+        <v>1536</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>384.7666510627297</v>
+        <v>467.7749065220658</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11</v>
+        <v>51.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>52.85143311864272</v>
+        <v>54.57796318786962</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>23.30663987437248</v>
+        <v>13.74567674043254</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7952850740952428</v>
+        <v>0.6604711957867274</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0164691298119445</v>
+        <v>0.3112866670503917</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1435</v>
+        <v>1442</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>380.7183489847618</v>
+        <v>463.9961152194388</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>24.65</v>
+        <v>30.05</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.16748534252914</v>
+        <v>59.77732465251191</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7.8875490254507</v>
+        <v>24.51200846444699</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.012777007365202</v>
+        <v>0.569529655563828</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1133467780403024</v>
+        <v>-0.0417638271701314</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1301</v>
+        <v>1466</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>377.3268795199679</v>
+        <v>463.9799855036687</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>55.6</v>
+        <v>17</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46.74057285264729</v>
+        <v>55.11409813460498</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.2879639242656</v>
+        <v>14.71294961773311</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2362339721304926</v>
+        <v>0.3900230198637866</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.826125254648997</v>
+        <v>-0.068655337603724</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1529</v>
+        <v>1434</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>375.3317305779123</v>
+        <v>460.1066782281397</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>17.15</v>
+        <v>17.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>30.08471933143115</v>
+        <v>49.32733178186417</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>35.58055901519018</v>
+        <v>27.25084531355139</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4782492879536094</v>
+        <v>0.31224132678664</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0234889353503895</v>
+        <v>-0.1668983153701756</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1312</v>
+        <v>1531</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>374.406842402978</v>
+        <v>452.2083128805055</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>11.9</v>
+        <v>13</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>43.60015075934464</v>
+        <v>53.26214078847718</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15.03698405684349</v>
+        <v>11.47833898706163</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3408073090038997</v>
+        <v>0.6918913080505323</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0116080394501703</v>
+        <v>-0.0068493873760168</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1437</v>
+        <v>1340</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>372.0820675344497</v>
+        <v>450.2045376049264</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>30.3</v>
+        <v>5.26</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>47.24111028021072</v>
+        <v>50.58992665982871</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.3630530643049</v>
+        <v>15.16164869552063</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.753519599408532</v>
+        <v>2.447087424038074</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.193574602873398</v>
+        <v>0.0117913592277117</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1438</v>
+        <v>1535</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>324.0965284716901</v>
+        <v>444.2170108398715</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>22.45</v>
+        <v>46.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.23340089418358</v>
+        <v>42.69629348956803</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.78726608230943</v>
+        <v>20.06099193453974</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3402546487611793</v>
+        <v>0.4324318036861196</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0225351541154804</v>
+        <v>0.0691872869860807</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1413</v>
+        <v>1402</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>321.3740315915614</v>
+        <v>431.4865867818972</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>9.4</v>
+        <v>27.25</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>47.89861371233631</v>
+        <v>48.53208252447895</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.62921728477176</v>
+        <v>14.98265544392255</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.0854226516112757</v>
+        <v>0.8748666103322199</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0490512913615632</v>
+        <v>0.007885730520667</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1443</v>
+        <v>1233</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>314.6002671919418</v>
+        <v>429.9782956728216</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>26.05</v>
+        <v>28.3</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.6034632756419</v>
+        <v>41.86551191468388</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10.12622783787222</v>
+        <v>33.6021529909022</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3891189433178434</v>
+        <v>2.619678594547713</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.046063069837107</v>
+        <v>-0.0725043229866663</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1215</v>
+        <v>1326</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>300.2774813873497</v>
+        <v>417.614022118259</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>109</v>
+        <v>58.8</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>48.76907489427433</v>
+        <v>46.72364786741233</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46.04018403637832</v>
+        <v>16.18149206215964</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.3217993286505418</v>
+        <v>0.3033480001258474</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.6135502568893485</v>
+        <v>-0.9563567661736904</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1342</v>
+        <v>1216</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>291.370998396547</v>
+        <v>406.1878362618413</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>103.5</v>
+        <v>75.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>44.21683810165703</v>
+        <v>48.45395477220026</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>29.00785181044808</v>
+        <v>22.4434292159452</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4239649555371862</v>
+        <v>0.464845413487146</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.5474151602430088</v>
+        <v>-0.3292378673129482</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1418</v>
+        <v>1321</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>289.2806165536698</v>
+        <v>405.1500315263117</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>18.05</v>
+        <v>32.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45.49146964423041</v>
+        <v>55.99938031814563</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.9064854849193</v>
+        <v>15.70932028320646</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.07830503393133439</v>
+        <v>0.8976667640478442</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0469534663168616</v>
+        <v>-0.0642099183046726</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1308</v>
+        <v>1568</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>288.4512213290426</v>
+        <v>404.8043427051909</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>13.65</v>
+        <v>28.6</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.69402639609014</v>
+        <v>41.83522428886447</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.90943347724968</v>
+        <v>23.48946534300345</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9394717782465584</v>
+        <v>0.3539803691980679</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0128151509991398</v>
+        <v>0.3894316544837957</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1582</v>
+        <v>1560</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>285.8165387100873</v>
+        <v>400.8347357455701</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>74.3</v>
+        <v>688</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.28894164681002</v>
+        <v>51.79926072947235</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>35.70489541579746</v>
+        <v>13.36942747825273</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.051136203223205</v>
+        <v>0.4741625760232691</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.446122500228832</v>
+        <v>3.599690437585213</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1256</v>
+        <v>1467</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>283.4451366287824</v>
+        <v>400.5006060059053</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>178</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>44.11878537641922</v>
+        <v>56.75644467681434</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11.75509477151438</v>
+        <v>18.30029682107356</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3916138227250977</v>
+        <v>0.4028030476834224</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.5336924677622172</v>
+        <v>-0.07109102824776781</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1419</v>
+        <v>1325</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>278.4306610938816</v>
+        <v>399.9170857301813</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>65</v>
+        <v>26.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>44.28948633132432</v>
+        <v>54.47035041618717</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.86836438969267</v>
+        <v>24.42973529382042</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3417338476106033</v>
+        <v>0.641140510517171</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.4421405839060781</v>
+        <v>0.0417923298712714</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1309</v>
+        <v>1468</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>276.0583100116261</v>
+        <v>397.9058360873087</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>12.9</v>
+        <v>13.55</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40.23723956517194</v>
+        <v>54.54455687386226</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.40296942710064</v>
+        <v>32.29357225568403</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2917132280238245</v>
+        <v>0.790169614439386</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0317117757529852</v>
+        <v>-0.0481706558958541</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1109</v>
+        <v>1203</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>273.1043222575728</v>
+        <v>396.2487646111425</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>13.55</v>
+        <v>46.15</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>29.25601556227792</v>
+        <v>47.85060401342729</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>38.67690665450619</v>
+        <v>16.55332518785111</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5623734142682579</v>
+        <v>0.4412605718888441</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0075967220492447</v>
+        <v>-0.2593357108609584</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1213</v>
+        <v>1409</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>269.9862107493723</v>
+        <v>392.597525396081</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>7.72</v>
+        <v>24.75</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.29196479701656</v>
+        <v>55.13721254424407</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.60638766894242</v>
+        <v>19.44434047033464</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.257765099407753</v>
+        <v>0.4383257877322477</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.4108208744957045</v>
+        <v>0.1834661644622681</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1229</v>
+        <v>1527</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>266.8431304128908</v>
+        <v>387.1657384589012</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>40.7</v>
+        <v>32.65</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.8075920985071</v>
+        <v>41.02707773288859</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>10.17510902778888</v>
+        <v>20.61240225051617</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3668009590548337</v>
+        <v>0.39664438079427</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.004669408092247</v>
+        <v>-0.1347033191569397</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1218</v>
+        <v>1526</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>258.2295530518275</v>
+        <v>385.2116733596049</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>15.8</v>
+        <v>18.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.91868576962771</v>
+        <v>59.21673561238784</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>40.21346199077008</v>
+        <v>46.94585414935807</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4444602904018371</v>
+        <v>0.580776968313254</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0402106245470759</v>
+        <v>0.0424008661320503</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1102</v>
+        <v>1416</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>250.466188886066</v>
+        <v>384.7666510627297</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>32.95</v>
+        <v>11</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.23102006485762</v>
+        <v>52.85143311864272</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>28.49622213452004</v>
+        <v>23.30663987437248</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.313168107561326</v>
+        <v>0.7952850740952428</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0543479796197455</v>
+        <v>0.0164691298119445</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1220</v>
+        <v>1435</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>250.0020168119005</v>
+        <v>380.7183489847618</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>11.15</v>
+        <v>24.65</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>33.45802895655817</v>
+        <v>54.16748534252914</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>35.44293262152075</v>
+        <v>7.8875490254507</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9209070604473454</v>
+        <v>1.012777007365202</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-8.611168073738296e-05</v>
+        <v>-0.1133467780403024</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1227</v>
+        <v>1301</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>245.8381839877155</v>
+        <v>377.3268795199679</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>29.2</v>
+        <v>55.6</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.0717040356772</v>
+        <v>46.74057285264729</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.0434971226909</v>
+        <v>16.2879639242656</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5514271137051873</v>
+        <v>0.2362339721304926</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0781972547635859</v>
+        <v>-0.826125254648997</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1441</v>
+        <v>1529</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>245.1699671627625</v>
+        <v>375.3317305779123</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>17.15</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>41.27370742422021</v>
+        <v>30.08471933143115</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.70694282646247</v>
+        <v>35.58055901519018</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5856204627494499</v>
+        <v>0.4782492879536094</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0025880711780282</v>
+        <v>0.0234889353503895</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1446</v>
+        <v>1312</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>243.9403894154929</v>
+        <v>374.406842402978</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>13.95</v>
+        <v>11.9</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>36.88155938031392</v>
+        <v>43.60015075934464</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>39.93857748087994</v>
+        <v>15.03698405684349</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5950848537824609</v>
+        <v>0.3408073090038997</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.08705160266745191</v>
+        <v>-0.0116080394501703</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1307</v>
+        <v>1437</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>243.0278649444217</v>
+        <v>372.0820675344497</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>30.9</v>
+        <v>30.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>40.06328869661023</v>
+        <v>47.24111028021072</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.96074060681871</v>
+        <v>20.3630530643049</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3.016380842202621</v>
+        <v>0.753519599408532</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.08256759283866261</v>
+        <v>-0.193574602873398</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1219</v>
+        <v>1472</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>232.9414892178733</v>
+        <v>366.4163875053413</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>27.77038990431721</v>
+        <v>51.7164746881626</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32.71663158633552</v>
+        <v>10.29541949249131</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7632866989878225</v>
+        <v>0.0993354650464071</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0714440395496822</v>
+        <v>1.289124285613736</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1104</v>
+        <v>1514</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>232.7995242119793</v>
+        <v>363.6186421050177</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>26.65</v>
+        <v>102</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.87824843189272</v>
+        <v>43.17686012403858</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.9596395864901</v>
+        <v>25.97785926740444</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.843243082377041</v>
+        <v>0.3168205530716353</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0295127971626206</v>
+        <v>0.5446821632476526</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1305</v>
+        <v>1475</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>226.9142858345361</v>
+        <v>349.8601471807221</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>11.7</v>
+        <v>27.15</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>44.97214551229173</v>
+        <v>51.1692364591933</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.97826173299758</v>
+        <v>11.02512044553161</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3470142229252547</v>
+        <v>1.686657122577385</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0196150097396708</v>
+        <v>0.0058837188686939</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1231</v>
+        <v>1456</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>224.5097175152215</v>
+        <v>339.9947522869889</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>80.3</v>
+        <v>14.25</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>31.87408791399382</v>
+        <v>55.29907544919909</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25.98211034398228</v>
+        <v>12.22257002089292</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3953534595738895</v>
+        <v>1.083257798382301</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.995768995764412</v>
+        <v>0.0506197359317037</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1338</v>
+        <v>1528</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>219.9430965182523</v>
+        <v>325.1117577943598</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>15.45</v>
+        <v>19</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.78504905153831</v>
+        <v>42.0403925928308</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>35.16739006497221</v>
+        <v>43.04452059913964</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.142809366382123</v>
+        <v>0.5699754698008188</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0130538811846954</v>
+        <v>0.2575480476479856</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1225</v>
+        <v>1513</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>211.1993201327839</v>
+        <v>324.2229869852226</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>25</v>
+        <v>159.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>38.86130286821421</v>
+        <v>47.6690273947666</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>33.55389528715855</v>
+        <v>22.61366654722094</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7875814786139048</v>
+        <v>0.4564830819627048</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.09092394921692599</v>
+        <v>0.7513561986088391</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>208.5972347698317</v>
+        <v>324.0965284716901</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>7.26</v>
+        <v>22.45</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>42.16042728975016</v>
+        <v>52.23340089418358</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.18754672831286</v>
+        <v>16.78726608230943</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4560211467935046</v>
+        <v>0.3402546487611793</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0712719406507603</v>
+        <v>0.0225351541154804</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1314</v>
+        <v>1413</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>199.6871860740196</v>
+        <v>321.3740315915614</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>7.74</v>
+        <v>9.4</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.48497000722318</v>
+        <v>47.89861371233631</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.00316718961778</v>
+        <v>17.62921728477176</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.050157422568513</v>
+        <v>0.0854226516112757</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0427690497566308</v>
+        <v>-0.0490512913615632</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1447</v>
+        <v>1504</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>199.607444136403</v>
+        <v>316.3781351272651</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>7.17</v>
+        <v>67.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,49 +3838,49 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.86790841357237</v>
+        <v>50.95803514304393</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.43821484954216</v>
+        <v>11.84301909546548</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5361979764636715</v>
+        <v>0.5671647926866603</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0678063562122455</v>
+        <v>0.3985748316781774</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1217</v>
+        <v>1443</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>179.9396072121974</v>
+        <v>314.6002671919418</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>9.84</v>
+        <v>26.05</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.39555803639406</v>
+        <v>48.6034632756419</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.93618935610581</v>
+        <v>10.12622783787222</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5581095265827097</v>
+        <v>0.3891189433178434</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.022520464982911</v>
+        <v>-0.046063069837107</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1108</v>
+        <v>1519</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>174.5345241714738</v>
+        <v>305.8465287054831</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>12.1</v>
+        <v>671</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>34.41076451086226</v>
+        <v>42.41158952635923</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>55.36989798129499</v>
+        <v>28.75746765466067</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8113937266295244</v>
+        <v>0.6642155709013335</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0474161179808466</v>
+        <v>1.512317058241376</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1436</v>
+        <v>1533</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>171.6052586390423</v>
+        <v>303.6641600780317</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>37.35</v>
+        <v>33.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>36.65199757600755</v>
+        <v>44.96251101316459</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>38.00720489137337</v>
+        <v>30.0669618521249</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3856345435295237</v>
+        <v>1.414371561549499</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.035652015987003</v>
+        <v>0.1891183290330723</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1471</v>
+        <v>1215</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>158.7118920932218</v>
+        <v>300.2774813873497</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>9.529999999999999</v>
+        <v>109</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>40.13540684741768</v>
+        <v>48.76907489427433</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>30.38319359370931</v>
+        <v>46.04018403637832</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5002555998375006</v>
+        <v>0.3217993286505418</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0314117826080745</v>
+        <v>0.6135502568893485</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1310</v>
+        <v>1524</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>156.2236749125234</v>
+        <v>291.7360034563691</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>8.08</v>
+        <v>27.15</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.86156533978302</v>
+        <v>49.60872611643097</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>25.47141747180627</v>
+        <v>30.18829916729987</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5984649742506316</v>
+        <v>0.875147230948066</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0797768376223008</v>
+        <v>0.2321115829640808</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1417</v>
+        <v>1342</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>147.9698196550612</v>
+        <v>291.370998396547</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>103.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>41.64525589946581</v>
+        <v>44.21683810165703</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.56455094982805</v>
+        <v>29.00785181044808</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4027821031869614</v>
+        <v>0.4239649555371862</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0191155766993819</v>
+        <v>-0.5474151602430088</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1324</v>
+        <v>1418</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>145.9356377683807</v>
+        <v>289.2806165536698</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>10.05</v>
+        <v>18.05</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.73859757124411</v>
+        <v>45.49146964423041</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.95891146280975</v>
+        <v>20.9064854849193</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6255134998486527</v>
+        <v>0.07830503393133439</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0052202098945228</v>
+        <v>-0.0469534663168616</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1569</v>
+        <v>1308</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>130.4734534793553</v>
+        <v>288.4512213290426</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>42.8</v>
+        <v>13.65</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.83858461925863</v>
+        <v>50.69402639609014</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.14611431496472</v>
+        <v>15.90943347724968</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.1998816790266702</v>
+        <v>0.9394717782465584</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.5179042610389324</v>
+        <v>0.0128151509991398</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1304</v>
+        <v>1503</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>127.8085342397576</v>
+        <v>287.5195043111385</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>12.1</v>
+        <v>195.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.31273272304497</v>
+        <v>42.132630185614</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.91914215687644</v>
+        <v>27.57388656296097</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.473317417440935</v>
+        <v>0.5205583736339958</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0068070893827432</v>
+        <v>0.4934480046803884</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1316</v>
+        <v>1582</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>126.8937502594822</v>
+        <v>285.8165387100873</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>10.05</v>
+        <v>74.3</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.41944271004673</v>
+        <v>50.28894164681002</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.65139964539589</v>
+        <v>35.70489541579746</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6784657644414619</v>
+        <v>1.051136203223205</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0221929073989992</v>
+        <v>1.446122500228832</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1423</v>
+        <v>1256</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>113.3934304045662</v>
+        <v>283.4451366287824</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>35.95</v>
+        <v>178</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.49654951178776</v>
+        <v>44.11878537641922</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.32724214360599</v>
+        <v>11.75509477151438</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.1583397159536261</v>
+        <v>0.3916138227250977</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.162432418309294</v>
+        <v>-0.5336924677622172</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1201</v>
+        <v>1506</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>108.3261391825892</v>
+        <v>283.3261387596981</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.15</v>
+        <v>10.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.34153673638144</v>
+        <v>51.17493080517829</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.99755037619781</v>
+        <v>23.52701872264269</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5234775377026394</v>
+        <v>1.083977083971008</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0335802860264326</v>
+        <v>-0.0357127458480727</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1103</v>
+        <v>1464</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>95.61966897669269</v>
+        <v>283.0649680847349</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46.84546754370454</v>
+        <v>49.37862875258937</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10.23609066997606</v>
+        <v>12.40783265754652</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3869830144951806</v>
+        <v>0.8557306713035857</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0128442084784236</v>
+        <v>-0.0062496728966701</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1410</v>
+        <v>1419</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>75.51857357338592</v>
+        <v>278.4306610938816</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>25.8</v>
+        <v>65</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.90140683300331</v>
+        <v>44.28948633132432</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.04508207501541</v>
+        <v>18.86836438969267</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.7234906401397504</v>
+        <v>0.3417338476106033</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,62 +4598,2871 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0141289588810439</v>
+        <v>-0.4421405839060781</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>巧新</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>277.8375569350126</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>43.79569464583879</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>17.28658179415105</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1.470578204211182</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-0.1413350920637204</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>台達化</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>276.0583100116261</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>40.23723956517194</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>17.40296942710064</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.2917132280238245</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-0.0317117757529852</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>信大</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>273.1043222575728</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>29.25601556227792</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>38.67690665450619</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.5623734142682579</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-0.0075967220492447</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>宏益</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>272.53804527442</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>49.70541174058715</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>21.56070525493503</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>1.149108471785315</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-0.0387139697589639</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>大飲</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>269.9862107493723</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>54.29196479701656</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>11.60638766894242</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>1.257765099407753</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>0.4108208744957045</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>川飛</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>268.7660046250556</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>29.32996916303696</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>56.61051752521329</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.7141285405674545</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>0.036560205688965</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>1229</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>聯華</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>266.8431304128908</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>47.8075920985071</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>10.17510902778888</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.3668009590548337</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.004669408092247</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>泰山</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>258.2295530518275</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>40.91868576962771</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>40.21346199077008</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.4444602904018371</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>0.0402106245470759</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>253.0713426330989</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46.54303012491582</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>10.09595419265627</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>1.241002521360708</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.0028982281949641</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>亞泥</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>250.466188886066</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>43.23102006485762</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>28.49622213452004</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.313168107561326</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.0543479796197455</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>台榮</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>250.0020168119005</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>33.45802895655817</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>35.44293262152075</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.9209070604473454</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-8.611168073738296e-05</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>1227</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>245.8381839877155</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>48.0717040356772</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>17.0434971226909</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.5514271137051873</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-0.0781972547635859</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>大東</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>245.1699671627625</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>41.27370742422021</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>13.70694282646247</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.5856204627494499</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-0.0025880711780282</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>宏和</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>243.9403894154929</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>36.88155938031392</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>39.93857748087994</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.5950848537824609</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>0.08705160266745191</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>三芳</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>243.0278649444217</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>40.06328869661023</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>18.96074060681871</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>3.016380842202621</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>0.08256759283866261</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>堤維西</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>234.1353401428369</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>45.19661407053747</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>23.07869861865257</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.9086147338069448</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>0.1319079126041417</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>福壽</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>232.9414892178733</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>27.77038990431721</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>32.71663158633552</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.7632866989878225</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-0.0714440395496822</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>環泥</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>232.7995242119793</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>44.87824843189272</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>15.9596395864901</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.843243082377041</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>0.0295127971626206</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>1532</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>勤美</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>228.3739052438991</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>40.21163566804709</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>27.48377503812901</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.5035327692787948</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-0.1234651953279521</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>1305</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>華夏</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>226.9142858345361</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>44.97214551229173</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>20.97826173299758</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.3470142229252547</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.0196150097396708</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>大億</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>225.35588765254</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>47.97796501483136</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>10.07518341762284</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.4287366882637735</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>0.033728478140989</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>1231</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>聯華食</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>224.5097175152215</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>31.87408791399382</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>25.98211034398228</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.3953534595738895</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-0.995768995764412</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>1338</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>廣華-KY</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>219.9430965182523</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>40.78504905153831</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>35.16739006497221</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>1.142809366382123</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-0.0130538811846954</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>福懋油</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>211.1993201327839</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>38.86130286821421</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>33.55389528715855</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.7875814786139048</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.09092394921692599</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>力麗</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>208.5972347698317</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>42.16042728975016</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>18.18754672831286</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.4560211467935046</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-0.0712719406507603</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>強盛新</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>207.991945057892</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>50.76088194108512</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>14.8167394142925</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.4341733568450631</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-0.006948352579218</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>1314</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>中石化</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>199.6871860740196</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>42.48497000722318</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>17.00316718961778</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.050157422568513</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-0.0427690497566308</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>力鵬</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>199.607444136403</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>47.86790841357237</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>18.43821484954216</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.5361979764636715</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-0.0678063562122455</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>宜進</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>192.0487638205085</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>41.86339650791077</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>15.8335937942792</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.6850945235481462</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.0220599379196323</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>1465</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>偉全</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>189.4294127515488</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>43.0576444908244</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>16.29144518610978</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.9129549811358983</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.0505312684332952</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>愛之味</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>179.9396072121974</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>45.39555803639406</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>13.93618935610581</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.5581095265827097</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-0.022520464982911</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>幸福</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>174.5345241714738</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>34.41076451086226</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>55.36989798129499</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.8113937266295244</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>0.0474161179808466</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>華友聯</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>171.6052586390423</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>36.65199757600755</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>38.00720489137337</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.3856345435295237</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-0.035652015987003</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>宏遠</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>170.4541957656101</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>40.98329909524027</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>18.83980739084251</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.4252015352218735</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.0158873217211047</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>大將</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>165.9210058694918</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>45.4797091797211</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>11.73743997185176</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>1.169250743119128</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.0071663305601247</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>亞崴</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>162.6924818444327</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>38.17826650479386</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>16.04067516024132</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>1.265428339906884</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>-0.1316768246327723</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>喬福</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>162.3826237727414</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>38.27061722878306</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>19.85652860551209</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.5786041107949988</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0649265348530027</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>錩泰</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>161.9758110463835</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>53.11993003396182</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>15.72111886229512</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.257719578542861</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0320155160279721</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>首利</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>158.7118920932218</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>40.13540684741768</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>30.38319359370931</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.5002555998375006</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.0314117826080745</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>1310</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>台苯</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>156.2236749125234</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>40.86156533978302</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>25.47141747180627</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.5984649742506316</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.0797768376223008</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>嘉裕</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>147.9698196550612</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>41.64525589946581</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>17.56455094982805</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.4027821031869614</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-0.0191155766993819</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>1324</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>地球</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>145.9356377683807</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>40.73859757124411</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>20.95891146280975</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.6255134998486527</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>-0.0052202098945228</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>正峰</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>136.9286692486996</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>41.2987594022824</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>10.80202407384853</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0.20748409360509</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>-0.8057095600721533</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>濱川</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>130.4734534793553</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>47.83858461925863</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>22.14611431496472</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.1998816790266702</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.5179042610389324</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>台聚</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>127.8085342397576</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>46.31273272304497</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>16.91914215687644</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.473317417440935</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>-0.0068070893827432</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>上曜</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>126.8937502594822</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>46.41944271004673</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>18.65139964539589</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.6784657644414619</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.0221929073989992</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>利華</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>113.3934304045662</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>41.49654951178776</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>14.32724214360599</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.1583397159536261</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.162432418309294</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>味全</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>108.3261391825892</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>43.34153673638144</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>14.99755037619781</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.5234775377026394</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0335802860264326</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>台富</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>98.92490862704636</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>47.64033557561956</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>13.07255500597023</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.980920530279335</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.0145986486995214</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>瑞利</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>95.62716965337351</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>39.00784373060181</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>8.16287252794978</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.6572700064246204</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.009451427329417301</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>嘉泥</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>95.61966897669269</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>46.84546754370454</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>10.23609066997606</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.3869830144951806</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.0128442084784236</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>弘裕</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>89.72239777675033</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>44.02569486509021</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>18.35981444589195</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>0.5430110537321322</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>-0.0391845374018095</v>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>南染</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>75.51857357338592</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>48.90140683300331</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>16.04508207501541</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.7234906401397504</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>-0.0141289588810439</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
         <v>1445</v>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>大宇</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D79" s="2" t="n">
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
         <v>65.61490006770882</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E132" s="2" t="n">
         <v>10.45</v>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="2" t="n">
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
         <v>39.49891678641576</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="I132" s="2" t="n">
         <v>15.31297395805671</v>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J132" s="2" t="n">
         <v>0.7311005453782687</v>
       </c>
-      <c r="K79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N79" s="2" t="n">
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
         <v>-0.0275302750137435</v>
       </c>
-      <c r="O79" s="2" t="inlineStr">
+      <c r="O132" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
